--- a/data/quarters/synthetic/malformed/2027Q1/SYNTHETIC_MALFORMED_prior_mark_unreconciled_Q1_2027.xlsx
+++ b/data/quarters/synthetic/malformed/2027Q1/SYNTHETIC_MALFORMED_prior_mark_unreconciled_Q1_2027.xlsx
@@ -1730,7 +1730,7 @@
         <v>43895</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>44477</v>
+        <v>46245</v>
       </c>
       <c r="H17" s="13" t="n">
         <v>176.3</v>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>hc-valuation engine 0.1.0, policy 2026Q4-0.1, run b9e1bcc61c42</t>
+          <t>hc-valuation engine 0.1.0, policy 2026Q4-0.1, run df62f01d0864</t>
         </is>
       </c>
     </row>
@@ -9441,7 +9441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9541,6 +9541,18 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>Entered the book in Q4 2026 from a New Investment row (M-014, X-918): fund, sector and stage are as that row named them, and the operating metrics (ARR, growth, margin, burn, cash, headcount) are blank because nothing is on file. Fill them before the next run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pellagrin</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>same-terms extension on 2026-08-11 is not price discovery; the staleness clock runs from 2021-10-08</t>
         </is>
       </c>
     </row>
